--- a/Checklist_Form 2.0 (1)/Checklist_Form 2.0/data/active/B001_FMS.xlsx
+++ b/Checklist_Form 2.0 (1)/Checklist_Form 2.0/data/active/B001_FMS.xlsx
@@ -722,7 +722,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1076,6 +1076,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1572,7 +1578,11 @@
           <t xml:space="preserve">Date </t>
         </is>
       </c>
-      <c r="E2" s="69" t="n"/>
+      <c r="E2" s="109" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
       <c r="F2" s="109" t="inlineStr">
         <is>
           <t>2026-04-08</t>
@@ -1594,7 +1604,11 @@
           <t>Condition</t>
         </is>
       </c>
-      <c r="E3" s="51" t="n"/>
+      <c r="E3" s="112" t="inlineStr">
+        <is>
+          <t>New Setup</t>
+        </is>
+      </c>
       <c r="F3" s="112" t="inlineStr">
         <is>
           <t>01</t>
@@ -1616,7 +1630,11 @@
           <t>Model Change From</t>
         </is>
       </c>
-      <c r="E4" s="51" t="n"/>
+      <c r="E4" s="112" t="inlineStr">
+        <is>
+          <t>S201</t>
+        </is>
+      </c>
       <c r="F4" s="112" t="inlineStr">
         <is>
           <t>12345</t>
@@ -1638,7 +1656,11 @@
           <t>Model to</t>
         </is>
       </c>
-      <c r="E5" s="51" t="n"/>
+      <c r="E5" s="112" t="inlineStr">
+        <is>
+          <t>S215</t>
+        </is>
+      </c>
       <c r="F5" s="112" t="inlineStr">
         <is>
           <t>432</t>
@@ -1660,7 +1682,11 @@
           <t>Shift</t>
         </is>
       </c>
-      <c r="E6" s="74" t="n"/>
+      <c r="E6" s="115" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="F6" s="115" t="inlineStr">
         <is>
           <t>B</t>
@@ -1706,7 +1732,11 @@
         </is>
       </c>
       <c r="D8" s="118" t="n"/>
-      <c r="E8" s="38" t="n"/>
+      <c r="E8" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="F8" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1730,7 +1760,11 @@
         </is>
       </c>
       <c r="D9" s="119" t="n"/>
-      <c r="E9" s="38" t="n"/>
+      <c r="E9" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="F9" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1754,7 +1788,11 @@
         </is>
       </c>
       <c r="D10" s="119" t="n"/>
-      <c r="E10" s="47" t="n"/>
+      <c r="E10" s="47" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="F10" s="47" t="inlineStr">
         <is>
           <t>NOT OK</t>
@@ -1800,7 +1838,11 @@
         </is>
       </c>
       <c r="D12" s="119" t="n"/>
-      <c r="E12" s="54" t="n"/>
+      <c r="E12" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="F12" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1824,7 +1866,11 @@
         </is>
       </c>
       <c r="D13" s="119" t="n"/>
-      <c r="E13" s="54" t="n"/>
+      <c r="E13" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="F13" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1848,7 +1894,11 @@
         </is>
       </c>
       <c r="D14" s="119" t="n"/>
-      <c r="E14" s="54" t="n"/>
+      <c r="E14" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="F14" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1876,7 +1926,11 @@
         </is>
       </c>
       <c r="D15" s="119" t="n"/>
-      <c r="E15" s="54" t="n"/>
+      <c r="E15" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="F15" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1900,7 +1954,11 @@
         </is>
       </c>
       <c r="D16" s="119" t="n"/>
-      <c r="E16" s="54" t="n"/>
+      <c r="E16" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="F16" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1924,7 +1982,11 @@
         </is>
       </c>
       <c r="D17" s="119" t="n"/>
-      <c r="E17" s="54" t="n"/>
+      <c r="E17" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="F17" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1952,7 +2014,11 @@
         </is>
       </c>
       <c r="D18" s="119" t="n"/>
-      <c r="E18" s="54" t="n"/>
+      <c r="E18" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="F18" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1994,7 +2060,11 @@
         </is>
       </c>
       <c r="D20" s="119" t="n"/>
-      <c r="E20" s="54" t="n"/>
+      <c r="E20" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="F20" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2020,7 +2090,11 @@
         </is>
       </c>
       <c r="D21" s="119" t="n"/>
-      <c r="E21" s="54" t="n"/>
+      <c r="E21" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="F21" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2046,7 +2120,11 @@
         </is>
       </c>
       <c r="D22" s="124" t="n"/>
-      <c r="E22" s="68" t="n"/>
+      <c r="E22" s="68" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="F22" s="68" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2070,7 +2148,11 @@
         </is>
       </c>
       <c r="D23" s="118" t="n"/>
-      <c r="E23" s="71" t="n"/>
+      <c r="E23" s="71" t="inlineStr">
+        <is>
+          <t>2026-05-07 08:00</t>
+        </is>
+      </c>
       <c r="F23" s="71" t="inlineStr">
         <is>
           <t>2026-04-08T11:51</t>
@@ -2092,7 +2174,11 @@
         </is>
       </c>
       <c r="D24" s="119" t="n"/>
-      <c r="E24" s="54" t="n"/>
+      <c r="E24" s="54" t="inlineStr">
+        <is>
+          <t>2026-05-07 09:30</t>
+        </is>
+      </c>
       <c r="F24" s="54" t="inlineStr">
         <is>
           <t>2026-04-08T11:51</t>
@@ -2114,7 +2200,11 @@
         </is>
       </c>
       <c r="D25" s="119" t="n"/>
-      <c r="E25" s="54" t="n"/>
+      <c r="E25" s="54" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
       <c r="F25" s="54" t="inlineStr">
         <is>
           <t>13</t>
@@ -2136,7 +2226,11 @@
         </is>
       </c>
       <c r="D26" s="119" t="n"/>
-      <c r="E26" s="54" t="n"/>
+      <c r="E26" s="54" t="inlineStr">
+        <is>
+          <t>John Operator (OP001)</t>
+        </is>
+      </c>
       <c r="F26" s="54" t="inlineStr">
         <is>
           <t>Hiba</t>
@@ -2158,7 +2252,11 @@
         </is>
       </c>
       <c r="D27" s="119" t="n"/>
-      <c r="E27" s="54" t="n"/>
+      <c r="E27" s="54" t="inlineStr">
+        <is>
+          <t>Supervisor Mike</t>
+        </is>
+      </c>
       <c r="F27" s="54" t="inlineStr">
         <is>
           <t>Sanika</t>
@@ -2180,7 +2278,11 @@
         </is>
       </c>
       <c r="D28" s="129" t="n"/>
-      <c r="E28" s="76" t="n"/>
+      <c r="E28" s="76" t="inlineStr">
+        <is>
+          <t>2026-05-07 14:11</t>
+        </is>
+      </c>
       <c r="F28" s="76" t="inlineStr">
         <is>
           <t>2026-04-08 11:52</t>
@@ -2194,14 +2296,9 @@
       <c r="L28" s="78" t="n"/>
     </row>
     <row r="29" ht="91.5" customFormat="1" customHeight="1" s="41" thickBot="1">
-      <c r="A29" s="80" t="inlineStr">
-        <is>
-          <t>a) Condition At set up change check list is being carried out     
-1) Set up change [Change of model (program &amp;  fixture)] 
-2) Machine break down
-3) Fixture wear part replacement/fixture modification 
-4) Development trial
-b) Reactivity Rule:- If any NC is found during set up inform to CC/Shift incharge wait for a dissision &amp; Raise  the break down intimation slip &amp; after the closure of NC, Do set up &amp; record observations in the set up change check list/Start up &amp; end check list (If applicable)</t>
+      <c r="A29" s="139" t="inlineStr">
+        <is>
+          <t>Verified</t>
         </is>
       </c>
       <c r="B29" s="130" t="n"/>
@@ -2217,14 +2314,9 @@
       <c r="L29" s="82" t="n"/>
     </row>
     <row r="30" hidden="1" ht="24" customFormat="1" customHeight="1" s="41">
-      <c r="A30" s="83" t="inlineStr">
-        <is>
-          <t>a) Condition at which set up change check list is being carried out     
-1) Set up change [Change of model (program &amp;  fixture)] 
-2) Machine break down
-3) Fixture wear part replacement/fixture modification 
-4) Development trial
-b) Reactivity Rule:- If any NC is found during set up inform to CC/Shift incharge wait for a dissision &amp; Raise  the break down intimation slip &amp; after the closure of NC, Do set up &amp; record observations in the set up change check list/Start up &amp; end check list (If applicable)</t>
+      <c r="A30" s="140" t="inlineStr">
+        <is>
+          <t>Supervisor Mike</t>
         </is>
       </c>
       <c r="B30" s="131" t="n"/>
@@ -2254,7 +2346,7 @@
       <c r="D31" s="133" t="n"/>
       <c r="E31" s="132" t="inlineStr">
         <is>
-          <t>Format &amp; Rev No</t>
+          <t>2026-05-07 14:11</t>
         </is>
       </c>
       <c r="F31" s="130" t="n"/>
